--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,6 +147,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3107,9 +3110,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
@@ -3687,9 +3690,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>225</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
@@ -3919,9 +3922,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
@@ -4035,9 +4038,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>242</t>
         </is>
       </c>
       <c r="U30" s="7" t="inlineStr">
@@ -4151,9 +4154,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -4267,9 +4270,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="U32" s="7" t="inlineStr">
@@ -4383,9 +4386,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T33" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>242,243</t>
         </is>
       </c>
       <c r="U33" s="7" t="inlineStr">
@@ -4499,9 +4502,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T34" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>242,243</t>
         </is>
       </c>
       <c r="U34" s="7" t="inlineStr">
@@ -4615,9 +4618,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T35" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>242,243</t>
         </is>
       </c>
       <c r="U35" s="7" t="inlineStr">
@@ -5195,9 +5198,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T40" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>310,311</t>
         </is>
       </c>
       <c r="U40" s="7" t="inlineStr">
@@ -5311,9 +5314,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>310,311</t>
         </is>
       </c>
       <c r="U41" s="7" t="inlineStr">
@@ -5427,9 +5430,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T42" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>312</t>
         </is>
       </c>
       <c r="U42" s="7" t="inlineStr">
@@ -5543,9 +5546,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T43" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>312</t>
         </is>
       </c>
       <c r="U43" s="7" t="inlineStr">
@@ -5659,9 +5662,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T44" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>315</t>
         </is>
       </c>
       <c r="U44" s="7" t="inlineStr">
@@ -5775,9 +5778,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>320,321</t>
         </is>
       </c>
       <c r="U45" s="7" t="inlineStr">
@@ -5891,9 +5894,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T46" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>320,321</t>
         </is>
       </c>
       <c r="U46" s="7" t="inlineStr">
@@ -6007,9 +6010,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>322,323</t>
         </is>
       </c>
       <c r="U47" s="7" t="inlineStr">
@@ -6123,9 +6126,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T48" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>322,323</t>
         </is>
       </c>
       <c r="U48" s="7" t="inlineStr">
@@ -6239,9 +6242,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>327</t>
         </is>
       </c>
       <c r="U49" s="7" t="inlineStr">
@@ -6355,9 +6358,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T50" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>331</t>
         </is>
       </c>
       <c r="U50" s="7" t="inlineStr">
@@ -6471,9 +6474,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>333</t>
         </is>
       </c>
       <c r="U51" s="7" t="inlineStr">
@@ -6587,9 +6590,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T52" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>339</t>
         </is>
       </c>
       <c r="U52" s="7" t="inlineStr">
@@ -7051,9 +7054,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T56" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>410,411,412</t>
         </is>
       </c>
       <c r="U56" s="7" t="inlineStr">
@@ -7167,9 +7170,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T57" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>411</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
@@ -7399,9 +7402,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T59" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>410,411</t>
         </is>
       </c>
       <c r="U59" s="7" t="inlineStr">
@@ -7515,9 +7518,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T60" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>420,421,422,425</t>
         </is>
       </c>
       <c r="U60" s="7" t="inlineStr">
@@ -7631,9 +7634,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>421,425</t>
         </is>
       </c>
       <c r="U61" s="7" t="inlineStr">
@@ -7747,9 +7750,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T62" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>420,421,422,425</t>
         </is>
       </c>
       <c r="U62" s="7" t="inlineStr">
@@ -7863,9 +7866,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T63" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>425,421</t>
         </is>
       </c>
       <c r="U63" s="7" t="inlineStr">
@@ -7979,9 +7982,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T64" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>430,431,432,435</t>
         </is>
       </c>
       <c r="U64" s="7" t="inlineStr">
@@ -8095,9 +8098,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T65" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>430,431,432,435</t>
         </is>
       </c>
       <c r="U65" s="7" t="inlineStr">
@@ -8211,9 +8214,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T66" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>435</t>
         </is>
       </c>
       <c r="U66" s="7" t="inlineStr">
@@ -8443,9 +8446,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T68" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>440,443,445</t>
         </is>
       </c>
       <c r="U68" s="7" t="inlineStr">
@@ -8559,9 +8562,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T69" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>445</t>
         </is>
       </c>
       <c r="U69" s="7" t="inlineStr">
@@ -8675,9 +8678,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T70" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>445</t>
         </is>
       </c>
       <c r="U70" s="7" t="inlineStr">
@@ -8791,9 +8794,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T71" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>453,455</t>
         </is>
       </c>
       <c r="U71" s="7" t="inlineStr">
@@ -9139,9 +9142,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T74" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>473,580</t>
         </is>
       </c>
       <c r="U74" s="7" t="inlineStr">
@@ -9255,9 +9258,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T75" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>473,580</t>
         </is>
       </c>
       <c r="U75" s="7" t="inlineStr">
@@ -9371,9 +9374,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T76" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>472,473,580</t>
         </is>
       </c>
       <c r="U76" s="7" t="inlineStr">
@@ -9487,9 +9490,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T77" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>490,491,580</t>
         </is>
       </c>
       <c r="U77" s="7" t="inlineStr">
@@ -10067,9 +10070,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T82" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>511</t>
         </is>
       </c>
       <c r="U82" s="7" t="inlineStr">
@@ -10188,9 +10191,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="U83" s="8" t="inlineStr">
+        <is>
+          <t>430,431,432,435</t>
         </is>
       </c>
       <c r="V83" s="7" t="inlineStr">
@@ -10304,9 +10307,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="U84" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="U84" s="8" t="inlineStr">
+        <is>
+          <t>430,431,432,435</t>
         </is>
       </c>
       <c r="V84" s="7" t="inlineStr">
@@ -10415,9 +10418,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T85" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>510,511,520,521</t>
         </is>
       </c>
       <c r="U85" s="7" t="inlineStr">
@@ -10531,9 +10534,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T86" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>510,511,520,521</t>
         </is>
       </c>
       <c r="U86" s="7" t="inlineStr">
@@ -10879,9 +10882,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T89" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>511</t>
         </is>
       </c>
       <c r="U89" s="7" t="inlineStr">
@@ -10995,9 +10998,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T90" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>521</t>
         </is>
       </c>
       <c r="U90" s="7" t="inlineStr">
@@ -11111,9 +11114,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T91" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>551,553,521,531,445</t>
         </is>
       </c>
       <c r="U91" s="7" t="inlineStr">
@@ -11227,9 +11230,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T92" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T92" s="8" t="inlineStr">
+        <is>
+          <t>551,553,521,531,445</t>
         </is>
       </c>
       <c r="U92" s="7" t="inlineStr">
@@ -11459,9 +11462,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T94" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T94" s="8" t="inlineStr">
+        <is>
+          <t>410,411,412</t>
         </is>
       </c>
       <c r="U94" s="7" t="inlineStr">
@@ -11575,9 +11578,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T95" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T95" s="8" t="inlineStr">
+        <is>
+          <t>580</t>
         </is>
       </c>
       <c r="U95" s="7" t="inlineStr">
@@ -11691,9 +11694,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T96" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T96" s="8" t="inlineStr">
+        <is>
+          <t>585,490</t>
         </is>
       </c>
       <c r="U96" s="7" t="inlineStr">
@@ -11807,9 +11810,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T97" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T97" s="8" t="inlineStr">
+        <is>
+          <t>590</t>
         </is>
       </c>
       <c r="U97" s="7" t="inlineStr">
@@ -11923,14 +11926,14 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T98" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U98" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T98" s="8" t="inlineStr">
+        <is>
+          <t>530,531</t>
+        </is>
+      </c>
+      <c r="U98" s="8" t="inlineStr">
+        <is>
+          <t>557,558</t>
         </is>
       </c>
       <c r="V98" s="7" t="inlineStr">
@@ -13199,9 +13202,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T109" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T109" s="8" t="inlineStr">
+        <is>
+          <t>710,711,713</t>
         </is>
       </c>
       <c r="U109" s="7" t="inlineStr">
@@ -13547,9 +13550,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T112" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T112" s="8" t="inlineStr">
+        <is>
+          <t>708</t>
         </is>
       </c>
       <c r="U112" s="7" t="inlineStr">
@@ -14011,9 +14014,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T116" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T116" s="8" t="inlineStr">
+        <is>
+          <t>722,721</t>
         </is>
       </c>
       <c r="U116" s="7" t="inlineStr">
@@ -14127,9 +14130,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T117" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T117" s="8" t="inlineStr">
+        <is>
+          <t>708</t>
         </is>
       </c>
       <c r="U117" s="7" t="inlineStr">
@@ -14475,9 +14478,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T120" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T120" s="8" t="inlineStr">
+        <is>
+          <t>731</t>
         </is>
       </c>
       <c r="U120" s="7" t="inlineStr">
@@ -14707,9 +14710,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T122" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T122" s="8" t="inlineStr">
+        <is>
+          <t>734</t>
         </is>
       </c>
       <c r="U122" s="7" t="inlineStr">
@@ -15171,9 +15174,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T126" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T126" s="8" t="inlineStr">
+        <is>
+          <t>729</t>
         </is>
       </c>
       <c r="U126" s="7" t="inlineStr">
@@ -15403,9 +15406,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T128" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T128" s="8" t="inlineStr">
+        <is>
+          <t>131,139</t>
         </is>
       </c>
       <c r="U128" s="7" t="inlineStr">
@@ -15519,9 +15522,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T129" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T129" s="8" t="inlineStr">
+        <is>
+          <t>733,731</t>
         </is>
       </c>
       <c r="U129" s="7" t="inlineStr">
@@ -15635,9 +15638,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T130" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T130" s="8" t="inlineStr">
+        <is>
+          <t>713,722,733,711,721,731</t>
         </is>
       </c>
       <c r="U130" s="7" t="inlineStr">
@@ -15751,9 +15754,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T131" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T131" s="8" t="inlineStr">
+        <is>
+          <t>733,731</t>
         </is>
       </c>
       <c r="U131" s="7" t="inlineStr">
@@ -15867,9 +15870,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T132" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T132" s="8" t="inlineStr">
+        <is>
+          <t>733,731</t>
         </is>
       </c>
       <c r="U132" s="7" t="inlineStr">
@@ -16795,9 +16798,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T140" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T140" s="8" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="U140" s="7" t="inlineStr">
@@ -16911,9 +16914,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T141" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T141" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
         </is>
       </c>
       <c r="U141" s="7" t="inlineStr">
@@ -17027,9 +17030,9 @@
           <t>AI CHOICE</t>
         </is>
       </c>
-      <c r="T142" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="T142" s="8" t="inlineStr">
+        <is>
+          <t>2034</t>
         </is>
       </c>
       <c r="U142" s="7" t="inlineStr">

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -8169,7 +8169,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
         <v>25</v>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H110" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>5</v>
       </c>
       <c r="H88" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H144" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6043,12 +6043,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AP Physics</t>
+          <t>AP Physics 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -6095,16 +6095,21 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AP Physics 1</t>
+          <t>AP Physics C</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6122,18 +6127,18 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>25</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6160,73 +6165,63 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AP Physics C</t>
+          <t>Introduction to Robotics</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Science</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>531</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>580</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Introduction to Robotics</t>
+          <t>Robotics Engineering</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6244,11 +6239,11 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11,9</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H101" t="n">
         <v>20</v>
@@ -6268,16 +6263,21 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Robotics Engineering</t>
+          <t>Robotics Design</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6295,11 +6295,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>10,11,9</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
         <v>20</v>
@@ -6321,19 +6321,19 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>580</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>590</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Robotics Design</t>
+          <t>Robotics Project</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6370,6 +6370,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Robotics Block</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6377,19 +6382,19 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Robotics Project</t>
+          <t>Robotics Project II</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6407,7 +6412,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6438,19 +6443,19 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>590</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>595</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Robotics Project II</t>
+          <t>Engineering Design</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6487,36 +6492,31 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Robotics Block</t>
-        </is>
-      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>590</t>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>530</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>610</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Engineering Design</t>
+          <t>Health/PE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Physical Education</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -6529,14 +6529,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H106" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6548,26 +6548,26 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Physical Education</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>530</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Health/PE</t>
+          <t>Driver's Ed/PE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6585,11 +6585,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H107" t="n">
         <v>25</v>
@@ -6618,12 +6618,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Driver's Ed/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6641,11 +6641,11 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H108" t="n">
         <v>25</v>
@@ -6674,12 +6674,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>642</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6697,11 +6697,11 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H109" t="n">
         <v>25</v>
@@ -6730,17 +6730,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>708</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>Introduction to Business</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Physical Education</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -6753,11 +6753,11 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H110" t="n">
         <v>25</v>
@@ -6772,48 +6772,43 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Physical Education</t>
-        </is>
-      </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>710</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Introduction to Business</t>
+          <t>World History</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>10,11,12,9</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H111" t="n">
         <v>25</v>
@@ -6826,6 +6821,11 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>World History</t>
+          <t>World History H</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H112" t="n">
         <v>25</v>
@@ -6893,12 +6893,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>World History H</t>
+          <t>AP World History</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6949,12 +6949,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>720</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AP World History</t>
+          <t>U.S. History I</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6972,11 +6972,11 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H114" t="n">
         <v>25</v>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7005,12 +7005,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U.S. History I</t>
+          <t>U.S. History I H</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
         <v>25</v>
@@ -7061,12 +7061,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U.S. History I H</t>
+          <t>Adv U.S. History I H</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7084,11 +7084,11 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
         <v>25</v>
@@ -7117,12 +7117,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>723</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Adv U.S. History I H</t>
+          <t>Introduction to Political Science</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7131,20 +7131,20 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
         <v>25</v>
@@ -7159,31 +7159,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
-        </is>
-      </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Introduction to Political Science</t>
+          <t>Business Concepts</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -7200,7 +7195,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H118" t="n">
         <v>25</v>
@@ -7217,19 +7212,19 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Business Concepts</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7275,12 +7270,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>AP Business with Personal Finance</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7289,20 +7284,20 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H120" t="n">
         <v>25</v>
@@ -7314,29 +7309,34 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>708</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AP Business with Personal Finance</t>
+          <t>U.S. History II</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -7349,11 +7349,11 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H121" t="n">
         <v>25</v>
@@ -7365,29 +7365,29 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>708</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U.S. History II</t>
+          <t>U.S. History II H</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7438,25 +7438,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U.S. History II H</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7480,11 +7480,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
-        </is>
-      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7494,30 +7489,30 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>AP U.S. History</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7533,46 +7528,56 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>722</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AP U.S. History</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H125" t="n">
         <v>25</v>
@@ -7584,39 +7589,34 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>728</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>741</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -7629,11 +7629,11 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -7650,46 +7650,41 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>728</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>742</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H127" t="n">
         <v>25</v>
@@ -7713,17 +7708,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>743</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>AP European History</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -7740,36 +7735,46 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
         <v>25</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>731</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>744</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AP European History</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7778,64 +7783,54 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" t="n">
         <v>25</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>731</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>745</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -7848,7 +7843,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -7867,26 +7862,36 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>734</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>751</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
+          <t>American Government &amp; Politics</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -7899,18 +7904,18 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
         <v>25</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7918,70 +7923,60 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>LEO II</t>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>734</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>752</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>American Government &amp; Politics</t>
+          <t>Economics H</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H132" t="n">
         <v>25</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -7993,25 +7988,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>756</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Economics H</t>
+          <t>Introduction to Law</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8020,14 +8015,14 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
         <v>25</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8037,48 +8032,48 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>757</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Introduction to Law</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H134" t="n">
         <v>25</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8088,19 +8083,24 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>729</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>758</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>International Business Strategies</t>
+          <t>Bloomberg Market Concepts</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8109,20 +8109,20 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135" t="n">
         <v>25</v>
@@ -8139,37 +8139,32 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>729</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>761</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bloomberg Market Concepts</t>
+          <t>AP Psychology</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8178,36 +8173,41 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
         <v>25</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>763</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AP Psychology</t>
+          <t>AP U.S. Government &amp; Politics</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8229,14 +8229,14 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137" t="n">
         <v>25</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8244,6 +8244,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8251,19 +8256,19 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>731</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AP U.S. Government &amp; Politics</t>
+          <t>AP Art History</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8281,18 +8286,18 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
         <v>25</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8305,26 +8310,26 @@
           <t>Social Studies</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>731</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AP Art History</t>
+          <t>AP Macroeconomics</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8333,27 +8338,27 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H139" t="n">
         <v>25</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8361,31 +8366,26 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>AP Art Block</t>
-        </is>
-      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>733</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AP Macroeconomics</t>
+          <t>AP Microeconomics</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8436,34 +8436,34 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>810</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>AP Microeconomics</t>
+          <t>Theology 9</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Theology</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H141" t="n">
         <v>25</v>
@@ -8475,29 +8475,29 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Theology</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>733</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>820</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Theology 9</t>
+          <t>Theology 10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -8548,12 +8548,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>830</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Theology 10</t>
+          <t>Theology 11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8571,11 +8571,11 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H143" t="n">
         <v>25</v>
@@ -8604,12 +8604,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>849</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Theology 11</t>
+          <t>Catholic Social Teaching</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8618,20 +8618,20 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H144" t="n">
         <v>25</v>
@@ -8660,12 +8660,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>851</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Catholic Social Teaching</t>
+          <t>Spirituality of Vocation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8716,37 +8716,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>955</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spirituality of Vocation</t>
+          <t>Academic Support</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Theology</t>
+          <t>Special Education</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H146" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -8758,63 +8758,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Theology</t>
-        </is>
-      </c>
       <c r="M146" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Academic Support</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Special Education</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>FY</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>10,11,12,9</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
-        <v>7</v>
-      </c>
-      <c r="H147" t="n">
-        <v>15</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H143" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Composition &amp; Literature</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -591,11 +596,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>25</v>
@@ -610,21 +615,26 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Composition &amp; Literature</t>
+          <t>Composition &amp; Literature H</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -646,7 +656,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>25</v>
@@ -675,12 +685,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Composition &amp; Literature H</t>
+          <t>Composition &amp; Literature</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,14 +712,14 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +741,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Composition &amp; Literature</t>
+          <t>American Literature</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -754,18 +764,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>25</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -787,12 +797,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Literature</t>
+          <t>American Literature H</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,7 +824,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>25</v>
@@ -843,12 +853,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Literature H</t>
+          <t>American Literature</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,14 +880,14 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -899,12 +909,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Literature</t>
+          <t>AP Seminar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -926,19 +936,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -955,12 +965,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AP Seminar</t>
+          <t>British Literature</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -978,11 +988,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>25</v>
@@ -994,7 +1004,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1011,12 +1021,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>British Literature</t>
+          <t>British Literature H</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1038,7 +1048,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -1067,12 +1077,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>British Literature H</t>
+          <t>British Literature</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1094,14 +1104,14 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1123,12 +1133,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>British Literature</t>
+          <t>AP English Language</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1150,19 +1160,19 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1179,12 +1189,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AP English Language</t>
+          <t>World Literature</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1202,11 +1212,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>25</v>
@@ -1218,7 +1228,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1235,12 +1245,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>World Literature</t>
+          <t>College English Honors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1291,12 +1301,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>College English Honors</t>
+          <t>Creative Writing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1305,37 +1315,32 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>25</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>English</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1347,12 +1352,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creative Writing</t>
+          <t>Public Speaking</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1370,18 +1375,18 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1398,12 +1403,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Public Speaking</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1421,18 +1426,18 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10,11,12,9</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>25</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1449,12 +1454,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Journalism</t>
+          <t>World Literature</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1463,16 +1468,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1491,6 +1496,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1500,12 +1510,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>World Literature</t>
+          <t>AP English Literature</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1527,19 +1537,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>25</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1556,73 +1566,73 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AP English Literature</t>
+          <t>Introduction to Guitar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,12,9</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>25</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Guitar Block</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Introduction to Guitar</t>
+          <t>Multi-Media Production</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Communication Arts</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1639,24 +1649,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Guitar Block</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1668,12 +1673,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Multi-Media Production</t>
+          <t>TV/Film Process and Principles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1691,7 +1696,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10,12,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1715,41 +1720,46 @@
           <t>N</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TV/Film Process and Principles</t>
+          <t>Guitar Ensemble</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Communication Arts</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1761,6 +1771,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Guitar Block</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>N</t>
@@ -1768,48 +1783,48 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guitar Ensemble</t>
+          <t>TV/Film Production &amp; Editing I</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Communication Arts</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1817,11 +1832,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Guitar Block</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>N</t>
@@ -1829,19 +1839,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TV/Film Production &amp; Editing I</t>
+          <t>TV/Film Production II</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1859,18 +1869,18 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>12</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1885,19 +1895,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2034</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TV/Film Production II</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1915,7 +1925,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1939,34 +1949,29 @@
           <t>N</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Digital Media</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Communication Arts</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1975,14 +1980,14 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1999,12 +2004,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>String Orchestra</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2018,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10,11,12,9</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2050,12 +2055,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>String Orchestra</t>
+          <t>Music Theory</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2064,23 +2069,23 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2101,17 +2106,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Music Theory</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Theater</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2124,7 +2129,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2152,17 +2157,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>Intermediate Theater</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Theater</t>
+          <t>Theater Arts</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2175,14 +2180,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10,11,12,9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2194,21 +2199,31 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Theater Block</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>226</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intermediate Theater</t>
+          <t>Adv Theater Production</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2226,7 +2241,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2264,17 +2279,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>241</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adv Theater Production</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Theater Arts</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2287,18 +2302,18 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2306,31 +2321,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Theater Block</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>226</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>Studio Art II</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2348,7 +2353,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10,11,12,9</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2367,21 +2372,31 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Studio Art Block</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Studio Art II</t>
+          <t>Studio Art III</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2399,7 +2414,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2430,19 +2445,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>242</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Studio Art III</t>
+          <t>Adv Drawing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2460,11 +2475,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>25</v>
@@ -2479,11 +2494,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Studio Art Block</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>N</t>
@@ -2491,19 +2501,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>241</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Adv Drawing</t>
+          <t>Adv Painting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2521,11 +2531,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>25</v>
@@ -2554,12 +2564,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Adv Painting</t>
+          <t>AP Drawing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2568,11 +2578,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2581,19 +2591,24 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>25</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2603,19 +2618,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>242</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>254</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AP Drawing</t>
+          <t>AP 2-D Art and Design</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2671,12 +2686,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AP 2-D Art and Design</t>
+          <t>AP 3-D Art and Design</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2732,17 +2747,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AP 3-D Art and Design</t>
+          <t>Spanish I</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>World Language</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2755,50 +2770,45 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,9</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>AP Art Block</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>World Language</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>242</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spanish I</t>
+          <t>Spanish I H</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2816,18 +2826,18 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10,11,9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2849,12 +2859,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spanish I H</t>
+          <t>Italian I</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2876,14 +2886,14 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>25</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2905,12 +2915,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Italian I</t>
+          <t>Latin I H</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2928,18 +2938,18 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2961,12 +2971,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Latin I H</t>
+          <t>Spanish II</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2984,18 +2994,18 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
         <v>25</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3011,18 +3021,23 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>310</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Spanish II</t>
+          <t>Spanish II H</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3040,11 +3055,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>25</v>
@@ -3071,19 +3086,19 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>311</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Spanish II H</t>
+          <t>Italian II</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3101,7 +3116,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3132,19 +3147,19 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>312</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Italian II</t>
+          <t>Italian II H</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3162,18 +3177,18 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>25</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3200,12 +3215,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Italian II H</t>
+          <t>Latin II H</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3223,7 +3238,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3254,19 +3269,19 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>315</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Latin II H</t>
+          <t>Spanish III</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3284,18 +3299,18 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
         <v>25</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3315,19 +3330,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>320</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spanish III</t>
+          <t>Spanish III H</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3345,7 +3360,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3376,19 +3391,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>321</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spanish III H</t>
+          <t>Italian III</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3406,18 +3421,18 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>25</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3437,19 +3452,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>322</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Italian III</t>
+          <t>Italian III H</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3491,6 +3506,11 @@
           <t>World Language</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Italian Block</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3498,19 +3518,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>323</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Italian III H</t>
+          <t>Latin III H</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3528,7 +3548,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11,9</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3552,11 +3572,6 @@
           <t>World Language</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Italian Block</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3564,19 +3579,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>327</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Latin III H</t>
+          <t>AP Spanish</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3594,23 +3609,23 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10,11,9</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
         <v>25</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3625,19 +3640,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>331</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AP Spanish</t>
+          <t>AP Italian</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3659,14 +3674,14 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>25</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3686,19 +3701,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>333</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AP Italian</t>
+          <t>AP Latin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3740,6 +3755,11 @@
           <t>World Language</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Italian Block</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3747,24 +3767,24 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>339</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AP Latin</t>
+          <t>Algebra I</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>World Language</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3777,55 +3797,45 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H59" t="n">
         <v>25</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>World Language</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Italian Block</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>339</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Algebra I</t>
+          <t>Algebra I H</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3847,14 +3857,14 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>25</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3876,12 +3886,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Algebra I H</t>
+          <t>Algebra I</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3903,14 +3913,14 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
         <v>25</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3932,12 +3942,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Algebra I</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3955,11 +3965,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H62" t="n">
         <v>25</v>
@@ -3982,18 +3992,23 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>410</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Geometry H</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4011,11 +4026,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
         <v>25</v>
@@ -4042,19 +4057,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>411</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Geometry H</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4072,11 +4087,11 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
         <v>25</v>
@@ -4103,19 +4118,19 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>Adv Geometry H</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4133,18 +4148,18 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>25</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4160,23 +4175,18 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>410</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adv Geometry H</t>
+          <t>Algebra II/Trig</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4194,18 +4204,18 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
         <v>25</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4221,18 +4231,23 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>420</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Algebra II/Trig</t>
+          <t>Algebra II/Trig H</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4250,11 +4265,11 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11,9</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
         <v>25</v>
@@ -4281,19 +4296,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>421</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Algebra II/Trig H</t>
+          <t>Algebra II/Trig</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4311,11 +4326,11 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10,11,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>25</v>
@@ -4342,19 +4357,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>420</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Algebra II/Trig</t>
+          <t>Adv Algebra II / Trig H</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4376,14 +4391,14 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>25</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4403,19 +4418,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>425</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adv Algebra II / Trig H</t>
+          <t>Precalculus</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4433,18 +4448,18 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
         <v>25</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4464,19 +4479,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>430</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Precalculus</t>
+          <t>AP Precalculus</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4494,11 +4509,11 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>25</v>
@@ -4510,7 +4525,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4525,19 +4540,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>431</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AP Precalculus</t>
+          <t>Adv Precalculus H</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4555,23 +4570,23 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>25</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4586,19 +4601,19 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>435</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Adv Precalculus H</t>
+          <t>Pre-college Math</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4616,18 +4631,18 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
         <v>25</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4643,23 +4658,18 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>435</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pre-college Math</t>
+          <t>Calculus H</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4677,7 +4687,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4706,16 +4716,21 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Calculus H</t>
+          <t>AP Calc AB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4737,19 +4752,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>25</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4764,19 +4779,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>443</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AP Calc AB</t>
+          <t>AP Calc BC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4832,12 +4847,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AP Calc BC</t>
+          <t>AP Statistics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4855,7 +4870,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4886,80 +4901,70 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>453</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AP Statistics</t>
+          <t>Web Design</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>25</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>453</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>Introduction to Programming</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4977,7 +4982,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4996,6 +5001,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Programming Block</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>N</t>
@@ -5005,68 +5015,68 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AP Computer Science A</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FY</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>25</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>473</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Introduction to Programming</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>10,11,12,9</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>2</v>
-      </c>
-      <c r="H80" t="n">
-        <v>25</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Programming Block</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AP Computer Science A</t>
+          <t>AP Computer Science Principles</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5084,7 +5094,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -5117,12 +5127,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AP Computer Science Principles</t>
+          <t>Applied Programming</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5131,11 +5141,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5156,7 +5166,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Programming Block</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5173,12 +5188,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>496</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Applied Programming</t>
+          <t>AP Cybersecurity</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5187,16 +5202,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5212,43 +5227,38 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Programming Block</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>490</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AP Cybersecurity</t>
+          <t>Earth Science</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5257,45 +5267,45 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Science</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>490</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Earth Science</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5304,7 +5314,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -5313,11 +5323,11 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H85" t="n">
         <v>25</v>
@@ -5346,12 +5356,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Biology H</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5369,11 +5379,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11,9</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H86" t="n">
         <v>25</v>
@@ -5402,12 +5412,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Biology H</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5425,14 +5435,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>10,11,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H87" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5452,18 +5462,23 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>510</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Chemistry H</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5485,10 +5500,10 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H88" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5512,19 +5527,19 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>511</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chemistry H</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5542,7 +5557,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5573,19 +5588,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>520</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Physics H</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5607,7 +5622,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H90" t="n">
         <v>25</v>
@@ -5634,19 +5649,19 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>521</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Physics H</t>
+          <t>Anatomy/Physiology</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5664,18 +5679,18 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>25</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5683,11 +5698,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5695,19 +5705,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>510,520</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Anatomy/Physiology</t>
+          <t>Anatomy/Physiology H</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5725,18 +5735,18 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>25</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5758,12 +5768,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Anatomy/Physiology H</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5781,18 +5791,18 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>25</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5807,19 +5817,19 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>510,520</t>
+          <t>510,520,530</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sports Medicine</t>
+          <t>Forensics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5841,14 +5851,14 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
         <v>25</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5859,23 +5869,18 @@
       <c r="M94" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>510,520,530</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Forensics</t>
+          <t>AP Biology</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5893,40 +5898,50 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>25</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Science</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>511</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>553</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AP Biology</t>
+          <t>AP Chemistry</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5944,7 +5959,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5975,19 +5990,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>521</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AP Chemistry</t>
+          <t>AP Physics 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6009,14 +6024,14 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
         <v>25</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6036,19 +6051,19 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>531</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AP Physics 1</t>
+          <t>AP Physics C</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6066,18 +6081,18 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>25</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6104,73 +6119,63 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AP Physics C</t>
+          <t>Introduction to Robotics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Science</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>531</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>580</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Introduction to Robotics</t>
+          <t>Robotics Engineering</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6188,11 +6193,11 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11,9</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H100" t="n">
         <v>20</v>
@@ -6212,16 +6217,21 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Robotics Engineering</t>
+          <t>Robotics Design</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6239,11 +6249,11 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>10,11,9</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H101" t="n">
         <v>20</v>
@@ -6265,19 +6275,19 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>580</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>590</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Robotics Design</t>
+          <t>Robotics Project</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6295,7 +6305,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6314,6 +6324,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Robotics Block</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6321,19 +6336,19 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Robotics Project</t>
+          <t>Robotics Project II</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6351,7 +6366,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6382,19 +6397,19 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>590</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>595</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Robotics Project II</t>
+          <t>Engineering Design</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6431,36 +6446,31 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Robotics Block</t>
-        </is>
-      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>590</t>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>530</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>610</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Engineering Design</t>
+          <t>Health/PE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Physical Education</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -6473,14 +6483,14 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6492,26 +6502,26 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Physical Education</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>530</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Health/PE</t>
+          <t>Driver's Ed/PE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6529,11 +6539,11 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H106" t="n">
         <v>25</v>
@@ -6562,12 +6572,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Driver's Ed/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6585,11 +6595,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H107" t="n">
         <v>25</v>
@@ -6618,12 +6628,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>642</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6641,11 +6651,11 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H108" t="n">
         <v>25</v>
@@ -6674,17 +6684,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>708</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>Introduction to Business</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Physical Education</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -6697,11 +6707,11 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H109" t="n">
         <v>25</v>
@@ -6716,48 +6726,43 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Physical Education</t>
-        </is>
-      </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>710</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Introduction to Business</t>
+          <t>World History</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10,11,12,9</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H110" t="n">
         <v>25</v>
@@ -6770,6 +6775,11 @@
       <c r="J110" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6781,12 +6791,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>World History</t>
+          <t>World History H</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6808,7 +6818,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
         <v>25</v>
@@ -6837,12 +6847,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>World History H</t>
+          <t>AP World History</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6876,7 +6886,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6893,12 +6903,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>720</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AP World History</t>
+          <t>U.S. History I</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6916,11 +6926,11 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H113" t="n">
         <v>25</v>
@@ -6932,7 +6942,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6949,12 +6959,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. History I</t>
+          <t>U.S. History I H</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6976,7 +6986,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H114" t="n">
         <v>25</v>
@@ -7005,12 +7015,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U.S. History I H</t>
+          <t>Adv U.S. History I H</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7028,11 +7038,11 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H115" t="n">
         <v>25</v>
@@ -7061,12 +7071,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>723</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adv U.S. History I H</t>
+          <t>Introduction to Political Science</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7075,20 +7085,20 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
         <v>25</v>
@@ -7103,31 +7113,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
-        </is>
-      </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Introduction to Political Science</t>
+          <t>Business Concepts</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -7144,7 +7149,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" t="n">
         <v>25</v>
@@ -7161,19 +7166,19 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Business Concepts</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7219,12 +7224,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>AP Business with Personal Finance</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7233,20 +7238,20 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H119" t="n">
         <v>25</v>
@@ -7258,29 +7263,34 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>708</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AP Business with Personal Finance</t>
+          <t>U.S. History II</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -7293,11 +7303,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H120" t="n">
         <v>25</v>
@@ -7309,29 +7319,29 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>708</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U.S. History II</t>
+          <t>U.S. History II H</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7382,25 +7392,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U.S. History II H</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7424,11 +7434,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
-        </is>
-      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7438,30 +7443,30 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>AP U.S. History</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7477,46 +7482,56 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>722</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AP U.S. History</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
         <v>25</v>
@@ -7528,39 +7543,34 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>728</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>741</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program I</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -7573,11 +7583,11 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125" t="n">
         <v>25</v>
@@ -7594,46 +7604,41 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>728</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>742</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -7657,17 +7662,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>743</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>AP European History</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -7684,36 +7689,46 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
         <v>25</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>731</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>744</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AP European History</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7722,64 +7737,54 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H128" t="n">
         <v>25</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>731</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>745</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -7792,7 +7797,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -7811,26 +7816,36 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>734</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>751</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Leadership, Entrepreneurship and Opportunity Program II</t>
+          <t>American Government &amp; Politics</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -7843,18 +7858,18 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
         <v>25</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7862,70 +7877,60 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>LEO II</t>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>734</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>752</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>American Government &amp; Politics</t>
+          <t>Economics H</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" t="n">
         <v>25</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -7937,25 +7942,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>756</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Economics H</t>
+          <t>Introduction to Law</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7964,14 +7969,14 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
         <v>25</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7981,48 +7986,48 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>757</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Introduction to Law</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H133" t="n">
         <v>25</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8032,19 +8037,24 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>729</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>758</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>International Business Strategies</t>
+          <t>Bloomberg Market Concepts</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8053,20 +8063,20 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
         <v>25</v>
@@ -8083,37 +8093,32 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>729</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>761</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bloomberg Market Concepts</t>
+          <t>AP Psychology</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8122,36 +8127,41 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
         <v>25</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>763</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AP Psychology</t>
+          <t>AP U.S. Government &amp; Politics</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8173,14 +8183,14 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136" t="n">
         <v>25</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8188,6 +8198,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8195,19 +8210,19 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>731</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AP U.S. Government &amp; Politics</t>
+          <t>AP Art History</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8225,18 +8240,18 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
         <v>25</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8249,26 +8264,26 @@
           <t>Social Studies</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>731</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AP Art History</t>
+          <t>AP Macroeconomics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8277,27 +8292,27 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
         <v>25</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8305,31 +8320,26 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Social Studies</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>AP Art Block</t>
-        </is>
-      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>733</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AP Macroeconomics</t>
+          <t>AP Microeconomics</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8380,34 +8390,34 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>810</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AP Microeconomics</t>
+          <t>Theology 9</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Theology</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H140" t="n">
         <v>25</v>
@@ -8419,29 +8429,29 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Theology</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>733</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>820</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Theology 9</t>
+          <t>Theology 10</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8459,7 +8469,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -8492,12 +8502,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>830</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Theology 10</t>
+          <t>Theology 11</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8515,7 +8525,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -8548,12 +8558,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>849</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Theology 11</t>
+          <t>Catholic Social Teaching</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8562,20 +8572,20 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H143" t="n">
         <v>25</v>
@@ -8604,12 +8614,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>851</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Catholic Social Teaching</t>
+          <t>Spirituality of Vocation</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8660,37 +8670,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>955</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spirituality of Vocation</t>
+          <t>Academic Support</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Theology</t>
+          <t>Special Education</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10,11,12,9</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -8702,63 +8712,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Theology</t>
-        </is>
-      </c>
       <c r="M145" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Academic Support</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Special Education</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>FY</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>10,11,12,9</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>7</v>
-      </c>
-      <c r="H146" t="n">
-        <v>15</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -7522,7 +7522,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H107" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>25</v>

--- a/templates/Template_7_Course_Profiles.xlsx
+++ b/templates/Template_7_Course_Profiles.xlsx
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>Tech Theater Level 1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
